--- a/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
@@ -2722,7 +2722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
@@ -2794,17 +2794,17 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -2816,22 +2816,22 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -2848,17 +2848,17 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -2875,17 +2875,17 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -2897,7 +2897,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -2924,7 +2924,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -2951,25 +2951,52 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Team</t>
         </is>

--- a/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Change Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Checklist'!$A$1:$L$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Checklist'!$A$1:$L$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -554,7 +554,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Al-Riyada College for Health Sciences · last updated 22 Oct 2026</t>
+          <t>Al-Riyada College for Health Sciences · last updated 23 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -664,23 +664,23 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$134,$A5)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$137,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$134,$A5,Checklist!$H$2:$H$134,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A5,Checklist!$H$2:$H$137,C$4)</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$134,$A5,Checklist!$H$2:$H$134,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A5,Checklist!$H$2:$H$137,D$4)</f>
         <v/>
       </c>
       <c r="E5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$134,$A5,Checklist!$H$2:$H$134,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A5,Checklist!$H$2:$H$137,E$4)</f>
         <v/>
       </c>
       <c r="F5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$134,$A5,Checklist!$H$2:$H$134,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A5,Checklist!$H$2:$H$137,F$4)</f>
         <v/>
       </c>
     </row>
@@ -691,23 +691,23 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$134,$A6)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$137,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$134,$A6,Checklist!$H$2:$H$134,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A6,Checklist!$H$2:$H$137,C$4)</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$134,$A6,Checklist!$H$2:$H$134,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A6,Checklist!$H$2:$H$137,D$4)</f>
         <v/>
       </c>
       <c r="E6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$134,$A6,Checklist!$H$2:$H$134,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A6,Checklist!$H$2:$H$137,E$4)</f>
         <v/>
       </c>
       <c r="F6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$134,$A6,Checklist!$H$2:$H$134,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A6,Checklist!$H$2:$H$137,F$4)</f>
         <v/>
       </c>
     </row>
@@ -718,23 +718,23 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$134,$A7)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$137,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$134,$A7,Checklist!$H$2:$H$134,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A7,Checklist!$H$2:$H$137,C$4)</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$134,$A7,Checklist!$H$2:$H$134,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A7,Checklist!$H$2:$H$137,D$4)</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$134,$A7,Checklist!$H$2:$H$134,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A7,Checklist!$H$2:$H$137,E$4)</f>
         <v/>
       </c>
       <c r="F7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$134,$A7,Checklist!$H$2:$H$134,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A7,Checklist!$H$2:$H$137,F$4)</f>
         <v/>
       </c>
     </row>
@@ -745,23 +745,23 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$134,$A8)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$137,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$134,$A8,Checklist!$H$2:$H$134,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A8,Checklist!$H$2:$H$137,C$4)</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$134,$A8,Checklist!$H$2:$H$134,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A8,Checklist!$H$2:$H$137,D$4)</f>
         <v/>
       </c>
       <c r="E8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$134,$A8,Checklist!$H$2:$H$134,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A8,Checklist!$H$2:$H$137,E$4)</f>
         <v/>
       </c>
       <c r="F8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$134,$A8,Checklist!$H$2:$H$134,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A8,Checklist!$H$2:$H$137,F$4)</f>
         <v/>
       </c>
     </row>
@@ -772,50 +772,77 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$134,$A9)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$137,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$134,$A9,Checklist!$H$2:$H$134,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A9,Checklist!$H$2:$H$137,C$4)</f>
         <v/>
       </c>
       <c r="D9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$134,$A9,Checklist!$H$2:$H$134,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A9,Checklist!$H$2:$H$137,D$4)</f>
         <v/>
       </c>
       <c r="E9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$134,$A9,Checklist!$H$2:$H$134,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A9,Checklist!$H$2:$H$137,E$4)</f>
         <v/>
       </c>
       <c r="F9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$134,$A9,Checklist!$H$2:$H$134,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A9,Checklist!$H$2:$H$137,F$4)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>6. Team and repository</t>
+        </is>
+      </c>
+      <c r="B10" s="7">
+        <f>COUNTIF(Checklist!$B$2:$B$137,$A10)</f>
+        <v/>
+      </c>
+      <c r="C10" s="7">
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A10,Checklist!$H$2:$H$137,C$4)</f>
+        <v/>
+      </c>
+      <c r="D10" s="7">
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A10,Checklist!$H$2:$H$137,D$4)</f>
+        <v/>
+      </c>
+      <c r="E10" s="7">
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A10,Checklist!$H$2:$H$137,E$4)</f>
+        <v/>
+      </c>
+      <c r="F10" s="7">
+        <f>COUNTIFS(Checklist!$B$2:$B$137,$A10,Checklist!$H$2:$H$137,F$4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B10" s="8">
-        <f>SUM(B5:B9)</f>
-        <v/>
-      </c>
-      <c r="C10" s="8">
-        <f>SUM(C5:C9)</f>
-        <v/>
-      </c>
-      <c r="D10" s="8">
-        <f>SUM(D5:D9)</f>
-        <v/>
-      </c>
-      <c r="E10" s="8">
-        <f>SUM(E5:E9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="8">
-        <f>SUM(F5:F9)</f>
+      <c r="B11" s="8">
+        <f>SUM(B5:B10)</f>
+        <v/>
+      </c>
+      <c r="C11" s="8">
+        <f>SUM(C5:C10)</f>
+        <v/>
+      </c>
+      <c r="D11" s="8">
+        <f>SUM(D5:D10)</f>
+        <v/>
+      </c>
+      <c r="E11" s="8">
+        <f>SUM(E5:E10)</f>
+        <v/>
+      </c>
+      <c r="F11" s="8">
+        <f>SUM(F5:F10)</f>
         <v/>
       </c>
     </row>
@@ -830,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -922,12 +949,12 @@
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>Pull the new branch</t>
+          <t>Pull develop</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>In apps/medical_hrms on the server: git fetch, then check out the branch named in the latest Change Log line.</t>
+          <t>In apps/medical_hrms on the server: git fetch, then check out develop (every branch merged into it on 23 Oct; see the latest Change Log line).</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
@@ -942,7 +969,7 @@
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>HR-58</t>
+          <t>HR-58, HR-71</t>
         </is>
       </c>
       <c r="H2" s="11" t="inlineStr">
@@ -958,7 +985,7 @@
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="L2" s="12" t="inlineStr"/>
@@ -2169,7 +2196,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Step 5: set the leave approver on each Department (Leave Approvers table) or on each Employee. 3 of 4 employees have none today.</t>
+          <t>Step 5: set the leave approver on each Department (Leave Approvers table) or on each Employee. Check the Leave setup check on the live server for how many have none.</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -2200,7 +2227,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr"/>
@@ -2691,9 +2718,171 @@
       </c>
       <c r="L34" s="12" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>CL-34</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>6. Team and repository</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Delete the merged branches on GitHub</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>After UAT: feature/uat-2026-10-22, feature/hr-portal-design, feature/jameah-ministry-views, fix/hrm-e2e-approval-permission-bugs, ministry-lookup, employee-applicant (all merged into develop; their history stays in develop).</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>After UAT</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>HR-71</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr"/>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="L35" s="12" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>CL-35</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>6. Team and repository</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Assign the open tasks</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Task Tracker, Tasks sheet: put a team member in the Owner column of each open task (e.g. HR-73, HR-16, HR-17, HR-25, JM-15, JM-19).</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>HR-73</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr"/>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="L36" s="12" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>CL-36</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>6. Team and repository</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Checks before every release</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>python3 tests/checks/files.py; fx.py tests/checks/site.py; python3 tests/checks/api_methods.py; then the browser suite (tests/e2e/README.md). All must pass.</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Developer (Abdul Hakeem)</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Every release</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>HR-72</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr"/>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="L37" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L34"/>
-  <conditionalFormatting sqref="H2:H134">
+  <autoFilter ref="A1:L37"/>
+  <conditionalFormatting sqref="H2:H137">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$H2="Open"</formula>
     </cfRule>
@@ -2708,7 +2897,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H134" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H2:H137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Open,Done,Blocked,Not needed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2722,7 +2911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2762,7 +2951,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -2772,12 +2961,12 @@
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
@@ -2799,12 +2988,12 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -2821,17 +3010,17 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -2843,22 +3032,22 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -2875,17 +3064,17 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -2902,17 +3091,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -2924,7 +3113,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -2934,12 +3123,12 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -2951,7 +3140,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -2961,12 +3150,12 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -2978,25 +3167,52 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Team</t>
         </is>

--- a/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
@@ -2911,7 +2911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2956,17 +2956,17 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
@@ -2978,7 +2978,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -3015,12 +3015,12 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -3037,17 +3037,17 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -3059,22 +3059,22 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -3091,17 +3091,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -3118,17 +3118,17 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -3140,7 +3140,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -3167,7 +3167,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -3194,25 +3194,52 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Team</t>
         </is>

--- a/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
@@ -148,30 +148,50 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FCF2C9"/>
+          <fgColor rgb="00EF6C00"/>
+          <bgColor rgb="00EF6C00"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00DDF0E6"/>
+          <fgColor rgb="002E7D32"/>
+          <bgColor rgb="002E7D32"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FBE1DE"/>
+          <fgColor rgb="00C62828"/>
+          <bgColor rgb="00C62828"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="001F2A27"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00ECE9E4"/>
+          <fgColor rgb="00B0BEC5"/>
+          <bgColor rgb="00B0BEC5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2883,16 +2903,16 @@
   </sheetData>
   <autoFilter ref="A1:L37"/>
   <conditionalFormatting sqref="H2:H137">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>$H2="Open"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
       <formula>$H2="Done"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
       <formula>$H2="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="1">
       <formula>$H2="Not needed"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2911,7 +2931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2961,12 +2981,12 @@
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>HR-04 - HR-06, HR-11, HR-28 - HR-30, HR-48, HR-66, HR-70, JM-12, JM-13, JM-16, JM-17, B-26</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Medical HRMS and Jameah are built by the HRMS team only, so no task is owned by the Education team (HR-11, HR-28, HR-48, JM-16, JM-17 now Abdul Hakeem; JM-12 Academic Affairs + Abdul Hakeem; JM-13 Registrar). Employee application: Dinesh + Abdul Hakeem built it (HR-06); Fathir handles its UI (HR-70) and Dinesh's open items (HR-04, HR-05). Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
@@ -2983,17 +3003,17 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -3005,7 +3025,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -3015,12 +3035,12 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -3042,12 +3062,12 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -3064,17 +3084,17 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -3086,22 +3106,22 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -3118,17 +3138,17 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -3145,17 +3165,17 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -3167,7 +3187,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -3177,12 +3197,12 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -3194,7 +3214,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -3204,12 +3224,12 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -3221,25 +3241,52 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Team</t>
         </is>

--- a/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
@@ -2697,12 +2697,12 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Developer copy of Education up to date</t>
+          <t>Developer copy of the education app up to date</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>On the development machine the Education checkout is behind its master branch; update it before testing there (git pull --ff-only).</t>
+          <t>On the development machine the education app checkout is behind its master branch; update it before testing there (git pull --ff-only).</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="L34" s="12" t="inlineStr"/>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>Task Tracker, Tasks sheet: put a team member in the Owner column of each open task (e.g. HR-73, HR-16, HR-17, HR-25, JM-15, JM-19).</t>
+          <t>Task Tracker, Tasks sheet: pick who each open task is given to in the Assigned to column (dropdown; e.g. HR-73, HR-16, HR-17, HR-25, JM-15, JM-19).</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -2981,12 +2981,12 @@
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>HR-04 - HR-06, HR-11, HR-28 - HR-30, HR-48, HR-66, HR-70, JM-12, JM-13, JM-16, JM-17, B-26</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>Owners corrected: Medical HRMS and Jameah are built by the HRMS team only, so no task is owned by the Education team (HR-11, HR-28, HR-48, JM-16, JM-17 now Abdul Hakeem; JM-12 Academic Affairs + Abdul Hakeem; JM-13 Registrar). Employee application: Dinesh + Abdul Hakeem built it (HR-06); Fathir handles its UI (HR-70) and Dinesh's open items (HR-04, HR-05). Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">

--- a/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Change Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Checklist'!$A$1:$L$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Checklist'!$A$1:$L$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -684,23 +684,23 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$137,$A5)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$138,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A5,Checklist!$H$2:$H$137,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A5,Checklist!$H$2:$H$138,C$4)</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A5,Checklist!$H$2:$H$137,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A5,Checklist!$H$2:$H$138,D$4)</f>
         <v/>
       </c>
       <c r="E5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A5,Checklist!$H$2:$H$137,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A5,Checklist!$H$2:$H$138,E$4)</f>
         <v/>
       </c>
       <c r="F5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A5,Checklist!$H$2:$H$137,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A5,Checklist!$H$2:$H$138,F$4)</f>
         <v/>
       </c>
     </row>
@@ -711,23 +711,23 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$137,$A6)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$138,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A6,Checklist!$H$2:$H$137,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A6,Checklist!$H$2:$H$138,C$4)</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A6,Checklist!$H$2:$H$137,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A6,Checklist!$H$2:$H$138,D$4)</f>
         <v/>
       </c>
       <c r="E6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A6,Checklist!$H$2:$H$137,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A6,Checklist!$H$2:$H$138,E$4)</f>
         <v/>
       </c>
       <c r="F6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A6,Checklist!$H$2:$H$137,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A6,Checklist!$H$2:$H$138,F$4)</f>
         <v/>
       </c>
     </row>
@@ -738,23 +738,23 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$137,$A7)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$138,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A7,Checklist!$H$2:$H$137,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A7,Checklist!$H$2:$H$138,C$4)</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A7,Checklist!$H$2:$H$137,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A7,Checklist!$H$2:$H$138,D$4)</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A7,Checklist!$H$2:$H$137,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A7,Checklist!$H$2:$H$138,E$4)</f>
         <v/>
       </c>
       <c r="F7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A7,Checklist!$H$2:$H$137,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A7,Checklist!$H$2:$H$138,F$4)</f>
         <v/>
       </c>
     </row>
@@ -765,23 +765,23 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$137,$A8)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$138,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A8,Checklist!$H$2:$H$137,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A8,Checklist!$H$2:$H$138,C$4)</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A8,Checklist!$H$2:$H$137,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A8,Checklist!$H$2:$H$138,D$4)</f>
         <v/>
       </c>
       <c r="E8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A8,Checklist!$H$2:$H$137,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A8,Checklist!$H$2:$H$138,E$4)</f>
         <v/>
       </c>
       <c r="F8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A8,Checklist!$H$2:$H$137,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A8,Checklist!$H$2:$H$138,F$4)</f>
         <v/>
       </c>
     </row>
@@ -792,23 +792,23 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$137,$A9)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$138,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A9,Checklist!$H$2:$H$137,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A9,Checklist!$H$2:$H$138,C$4)</f>
         <v/>
       </c>
       <c r="D9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A9,Checklist!$H$2:$H$137,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A9,Checklist!$H$2:$H$138,D$4)</f>
         <v/>
       </c>
       <c r="E9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A9,Checklist!$H$2:$H$137,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A9,Checklist!$H$2:$H$138,E$4)</f>
         <v/>
       </c>
       <c r="F9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A9,Checklist!$H$2:$H$137,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A9,Checklist!$H$2:$H$138,F$4)</f>
         <v/>
       </c>
     </row>
@@ -819,23 +819,23 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$137,$A10)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$138,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A10,Checklist!$H$2:$H$137,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A10,Checklist!$H$2:$H$138,C$4)</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A10,Checklist!$H$2:$H$137,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A10,Checklist!$H$2:$H$138,D$4)</f>
         <v/>
       </c>
       <c r="E10" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A10,Checklist!$H$2:$H$137,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A10,Checklist!$H$2:$H$138,E$4)</f>
         <v/>
       </c>
       <c r="F10" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$137,$A10,Checklist!$H$2:$H$137,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$138,$A10,Checklist!$H$2:$H$138,F$4)</f>
         <v/>
       </c>
     </row>
@@ -877,7 +877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2900,9 +2900,63 @@
       </c>
       <c r="L37" s="12" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>CL-37</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>5. Reviews and testing</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Share the guides</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>Give HR, managers and the testing team docs/guides/Medical_HRMS_Jameah_User_Guide.pdf, and the server admin docs/guides/Medical_HRMS_Jameah_Installation_Guide.pdf; collect their questions.</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>UAT</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>HR-74</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="inlineStr"/>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="L38" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L37"/>
-  <conditionalFormatting sqref="H2:H137">
+  <autoFilter ref="A1:L38"/>
+  <conditionalFormatting sqref="H2:H138">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>$H2="Open"</formula>
     </cfRule>
@@ -2917,7 +2971,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H2:H138" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Open,Done,Blocked,Not needed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2931,7 +2985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2976,17 +3030,17 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Project tracking</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
+          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
@@ -3008,12 +3062,12 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -3030,17 +3084,17 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -3052,7 +3106,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -3062,12 +3116,12 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -3089,12 +3143,12 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -3111,17 +3165,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -3133,22 +3187,22 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -3165,17 +3219,17 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -3192,17 +3246,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -3214,7 +3268,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -3224,12 +3278,12 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -3241,7 +3295,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -3251,12 +3305,12 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -3268,25 +3322,52 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Team</t>
         </is>

--- a/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Change Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Checklist'!$A$1:$L$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Checklist'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -684,23 +684,23 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$138,$A5)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$139,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A5,Checklist!$H$2:$H$138,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A5,Checklist!$H$2:$H$139,C$4)</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A5,Checklist!$H$2:$H$138,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A5,Checklist!$H$2:$H$139,D$4)</f>
         <v/>
       </c>
       <c r="E5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A5,Checklist!$H$2:$H$138,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A5,Checklist!$H$2:$H$139,E$4)</f>
         <v/>
       </c>
       <c r="F5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A5,Checklist!$H$2:$H$138,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A5,Checklist!$H$2:$H$139,F$4)</f>
         <v/>
       </c>
     </row>
@@ -711,23 +711,23 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$138,$A6)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$139,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A6,Checklist!$H$2:$H$138,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A6,Checklist!$H$2:$H$139,C$4)</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A6,Checklist!$H$2:$H$138,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A6,Checklist!$H$2:$H$139,D$4)</f>
         <v/>
       </c>
       <c r="E6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A6,Checklist!$H$2:$H$138,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A6,Checklist!$H$2:$H$139,E$4)</f>
         <v/>
       </c>
       <c r="F6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A6,Checklist!$H$2:$H$138,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A6,Checklist!$H$2:$H$139,F$4)</f>
         <v/>
       </c>
     </row>
@@ -738,23 +738,23 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$138,$A7)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$139,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A7,Checklist!$H$2:$H$138,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A7,Checklist!$H$2:$H$139,C$4)</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A7,Checklist!$H$2:$H$138,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A7,Checklist!$H$2:$H$139,D$4)</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A7,Checklist!$H$2:$H$138,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A7,Checklist!$H$2:$H$139,E$4)</f>
         <v/>
       </c>
       <c r="F7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A7,Checklist!$H$2:$H$138,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A7,Checklist!$H$2:$H$139,F$4)</f>
         <v/>
       </c>
     </row>
@@ -765,23 +765,23 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$138,$A8)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$139,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A8,Checklist!$H$2:$H$138,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A8,Checklist!$H$2:$H$139,C$4)</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A8,Checklist!$H$2:$H$138,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A8,Checklist!$H$2:$H$139,D$4)</f>
         <v/>
       </c>
       <c r="E8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A8,Checklist!$H$2:$H$138,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A8,Checklist!$H$2:$H$139,E$4)</f>
         <v/>
       </c>
       <c r="F8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A8,Checklist!$H$2:$H$138,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A8,Checklist!$H$2:$H$139,F$4)</f>
         <v/>
       </c>
     </row>
@@ -792,23 +792,23 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$138,$A9)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$139,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A9,Checklist!$H$2:$H$138,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A9,Checklist!$H$2:$H$139,C$4)</f>
         <v/>
       </c>
       <c r="D9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A9,Checklist!$H$2:$H$138,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A9,Checklist!$H$2:$H$139,D$4)</f>
         <v/>
       </c>
       <c r="E9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A9,Checklist!$H$2:$H$138,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A9,Checklist!$H$2:$H$139,E$4)</f>
         <v/>
       </c>
       <c r="F9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A9,Checklist!$H$2:$H$138,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A9,Checklist!$H$2:$H$139,F$4)</f>
         <v/>
       </c>
     </row>
@@ -819,23 +819,23 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$138,$A10)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$139,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A10,Checklist!$H$2:$H$138,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A10,Checklist!$H$2:$H$139,C$4)</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A10,Checklist!$H$2:$H$138,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A10,Checklist!$H$2:$H$139,D$4)</f>
         <v/>
       </c>
       <c r="E10" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A10,Checklist!$H$2:$H$138,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A10,Checklist!$H$2:$H$139,E$4)</f>
         <v/>
       </c>
       <c r="F10" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$138,$A10,Checklist!$H$2:$H$138,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A10,Checklist!$H$2:$H$139,F$4)</f>
         <v/>
       </c>
     </row>
@@ -877,7 +877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2093,7 +2093,7 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>CL-28</t>
+          <t>CL-38</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -2103,27 +2103,27 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Leave period for Al Riyada College</t>
+          <t>Exam committees with proctors</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>HR Portal &gt; Leave &gt; Yearly setup 1: Leave Period for this year, company Al Riyada College, tick Is Active.</t>
+          <t>Enter the exam committees (date, time, room) with their proctors; until then Proctor Schedules is empty. Needed to review HR requirement 2.</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Academic Affairs</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Before UAT</t>
+          <t>Before the HR review meeting</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>HR-69</t>
+          <t>HR-37</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
@@ -2134,12 +2134,12 @@
       <c r="I23" s="11" t="inlineStr"/>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr"/>
@@ -2147,7 +2147,7 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>CL-29</t>
+          <t>CL-28</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -2157,12 +2157,12 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Holiday list for Al Riyada College</t>
+          <t>Leave period for Al Riyada College</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Step 2: Holiday List with the official holidays and weekends; set it as the default holiday list on the Company.</t>
+          <t>HR Portal &gt; Leave &gt; Yearly setup 1: Leave Period for this year, company Al Riyada College, tick Is Active.</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>HR-69, DEC-10</t>
+          <t>HR-69</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>CL-30</t>
+          <t>CL-29</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -2211,12 +2211,12 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Leave approvers</t>
+          <t>Holiday list for Al Riyada College</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Step 5: set the leave approver on each Department (Leave Approvers table) or on each Employee. Check the Leave setup check on the live server for how many have none.</t>
+          <t>Step 2: Holiday List with the official holidays and weekends; set it as the default holiday list on the Company.</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>HR-69</t>
+          <t>HR-69, DEC-10</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr"/>
@@ -2255,7 +2255,7 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>CL-31</t>
+          <t>CL-30</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Annual leave balances</t>
+          <t>Leave approvers</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Steps 3-4: submit the annual leave policy (21 or 30 days) and assign it with Leave Control Panel; the Leave setup check turns green.</t>
+          <t>Step 5: set the leave approver on each Department (Leave Approvers table) or on each Employee. Check the Leave setup check on the live server for how many have none.</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="L26" s="12" t="inlineStr"/>
@@ -2309,7 +2309,7 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>CL-32</t>
+          <t>CL-31</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -2319,17 +2319,17 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Sick Leave policy</t>
+          <t>Annual leave balances</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Review and submit 'Medical HRMS - Sick Leave (3 Pay Stages, Separate Sick Year)'; Finance checks the 75% pay on a salary slip.</t>
+          <t>Steps 3-4: submit the annual leave policy (21 or 30 days) and assign it with Leave Control Panel; the Leave setup check turns green.</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>HR + Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>HR-20, DEC-14</t>
+          <t>HR-69</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -2363,7 +2363,7 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>CL-22</t>
+          <t>CL-32</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -2373,27 +2373,27 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Attendance devices</t>
+          <t>Sick Leave policy</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Connect the devices so Faculty After 4 PM uses real check-out times.</t>
+          <t>Review and submit 'Medical HRMS - Sick Leave (3 Pay Stages, Separate Sick Year)'; Finance checks the 75% pay on a salary slip.</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>HR + IT</t>
+          <t>HR + Finance</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>Later</t>
+          <t>Before UAT</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>HR-56</t>
+          <t>HR-20, DEC-14</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
@@ -2404,12 +2404,12 @@
       <c r="I28" s="11" t="inlineStr"/>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr"/>
@@ -2417,37 +2417,37 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>CL-23</t>
+          <t>CL-22</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>5. Reviews and testing</t>
+          <t>4. HR data</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Run the test cases</t>
+          <t>Attendance devices</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Testing team works through Medical_HRMS_Jameah_Test_Cases.xlsx and records results and bugs there.</t>
+          <t>Connect the devices so Faculty After 4 PM uses real check-out times.</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Testing team</t>
+          <t>HR + IT</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>UAT</t>
+          <t>Later</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>HR-46</t>
+          <t>HR-56</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
@@ -2471,7 +2471,7 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>CL-24</t>
+          <t>CL-23</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Arabic labels</t>
+          <t>Run the test cases</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>An Arabic speaker reads the HR / Employee Portal pages in Arabic and lists wording to change, including the 114 new leave texts (22 Oct).</t>
+          <t>Testing team works through Medical_HRMS_Jameah_Test_Cases.xlsx and records results and bugs there.</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Project owner</t>
+          <t>Testing team</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>HR-66, HR-68</t>
+          <t>HR-46</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr"/>
@@ -2525,7 +2525,7 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>CL-25</t>
+          <t>CL-24</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -2535,12 +2535,12 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Portal design approval</t>
+          <t>Arabic labels</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Client confirms the new HR Portal / Employee Portal look.</t>
+          <t>An Arabic speaker reads the HR / Employee Portal pages in Arabic and lists wording to change, including the 114 new leave texts (22 Oct).</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-66, HR-68</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr"/>
@@ -2579,7 +2579,7 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>CL-33</t>
+          <t>CL-25</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -2589,17 +2589,17 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Leave flow UAT</t>
+          <t>Portal design approval</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>An employee and their manager go through TC-LV-09 - TC-LV-17: plan, apply now, approve, return (also after sick leave).</t>
+          <t>Client confirms the new HR Portal / Employee Portal look.</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Testing team</t>
+          <t>Project owner</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>HR-68</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
@@ -2620,12 +2620,12 @@
       <c r="I32" s="11" t="inlineStr"/>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr"/>
@@ -2633,7 +2633,7 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>CL-26</t>
+          <t>CL-33</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Arabic interface</t>
+          <t>Leave flow UAT</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Switch to AR and repeat a few test cases (HR Portal, Employee Portal, application form).</t>
+          <t>An employee and their manager go through TC-LV-09 - TC-LV-17: plan, apply now, approve, return (also after sick leave).</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HR-68</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
@@ -2674,12 +2674,12 @@
       <c r="I33" s="11" t="inlineStr"/>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>CL-27</t>
+          <t>CL-26</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Developer copy of the education app up to date</t>
+          <t>Arabic interface</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>On the development machine the education app checkout is behind its master branch; update it before testing there (git pull --ff-only).</t>
+          <t>Switch to AR and repeat a few test cases (HR Portal, Employee Portal, application form).</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>Project owner</t>
+          <t>Testing team</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>Now</t>
+          <t>UAT</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="L34" s="12" t="inlineStr"/>
@@ -2741,22 +2741,22 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>CL-34</t>
+          <t>CL-27</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>6. Team and repository</t>
+          <t>5. Reviews and testing</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Delete the merged branches on GitHub</t>
+          <t>Developer copy of the education app up to date</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>After UAT: feature/uat-2026-10-22, feature/hr-portal-design, feature/jameah-ministry-views, fix/hrm-e2e-approval-permission-bugs, ministry-lookup, employee-applicant (all merged into develop; their history stays in develop).</t>
+          <t>On the development machine the education app checkout is behind its master branch; update it before testing there (git pull --ff-only).</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>After UAT</t>
+          <t>Now</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>HR-71</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
@@ -2782,7 +2782,7 @@
       <c r="I35" s="11" t="inlineStr"/>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
@@ -2795,7 +2795,7 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>CL-35</t>
+          <t>CL-34</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Assign the open tasks</t>
+          <t>Delete the merged branches on GitHub</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>Task Tracker, Tasks sheet: pick who each open task is given to in the Assigned to column (dropdown; e.g. HR-73, HR-16, HR-17, HR-25, JM-15, JM-19).</t>
+          <t>After UAT: feature/uat-2026-10-22, feature/hr-portal-design, feature/jameah-ministry-views, fix/hrm-e2e-approval-permission-bugs, ministry-lookup, employee-applicant (all merged into develop; their history stays in develop).</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>Now</t>
+          <t>After UAT</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>HR-73</t>
+          <t>HR-71</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
@@ -2849,7 +2849,7 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>CL-36</t>
+          <t>CL-35</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -2859,27 +2859,27 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Checks before every release</t>
+          <t>Assign the open tasks</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>python3 tests/checks/files.py; fx.py tests/checks/site.py; python3 tests/checks/api_methods.py; then the browser suite (tests/e2e/README.md). All must pass.</t>
+          <t>Task Tracker, Tasks sheet: pick who each open task is given to in the Assigned to column (dropdown; e.g. HR-73, HR-16, HR-17, HR-25, JM-15, JM-19).</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Developer (Abdul Hakeem)</t>
+          <t>Project owner</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>Every release</t>
+          <t>Now</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>HR-72</t>
+          <t>HR-73</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
@@ -2903,37 +2903,37 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>CL-37</t>
+          <t>CL-36</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>5. Reviews and testing</t>
+          <t>6. Team and repository</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Share the guides</t>
+          <t>Checks before every release</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>Give HR, managers and the testing team docs/guides/Medical_HRMS_Jameah_User_Guide.pdf, and the server admin docs/guides/Medical_HRMS_Jameah_Installation_Guide.pdf; collect their questions.</t>
+          <t>python3 tests/checks/files.py; fx.py tests/checks/site.py; python3 tests/checks/api_methods.py; then the browser suite (tests/e2e/README.md). All must pass.</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Project owner</t>
+          <t>Developer (Abdul Hakeem)</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>UAT</t>
+          <t>Every release</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>HR-74</t>
+          <t>HR-72</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
@@ -2954,9 +2954,63 @@
       </c>
       <c r="L38" s="12" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>CL-37</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>5. Reviews and testing</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Share the guides</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Give HR, managers and the testing team docs/guides/Medical_HRMS_Jameah_User_Guide.pdf, and the server admin docs/guides/Medical_HRMS_Jameah_Installation_Guide.pdf; collect their questions.</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>UAT</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>HR-74</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr"/>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="L39" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L38"/>
-  <conditionalFormatting sqref="H2:H138">
+  <autoFilter ref="A1:L39"/>
+  <conditionalFormatting sqref="H2:H139">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>$H2="Open"</formula>
     </cfRule>
@@ -2971,7 +3025,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H138" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H2:H139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Open,Done,Blocked,Not needed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2985,7 +3039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3035,12 +3089,12 @@
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
+          <t>HR-37, HR-38, DEC-15, CL-38</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
+          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
@@ -3057,17 +3111,17 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Project tracking</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
+          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -3089,12 +3143,12 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -3111,17 +3165,17 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -3133,7 +3187,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -3143,12 +3197,12 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -3170,12 +3224,12 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -3192,17 +3246,17 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -3214,22 +3268,22 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -3246,17 +3300,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -3273,17 +3327,17 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -3295,7 +3349,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -3305,12 +3359,12 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -3322,7 +3376,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -3332,12 +3386,12 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -3349,25 +3403,52 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Team</t>
         </is>

--- a/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
@@ -146,7 +146,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <font>
         <b val="1"/>
@@ -156,6 +156,18 @@
         <patternFill patternType="solid">
           <fgColor rgb="00EF6C00"/>
           <bgColor rgb="00EF6C00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="001565C0"/>
+          <bgColor rgb="001565C0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -574,7 +586,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Al-Riyada College for Health Sciences · last updated 23 Oct 2026</t>
+          <t>Al-Riyada College for Health Sciences · last updated 27 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -620,15 +632,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -663,15 +676,20 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Not needed</t>
         </is>
@@ -703,6 +721,10 @@
         <f>COUNTIFS(Checklist!$B$2:$B$139,$A5,Checklist!$H$2:$H$139,F$4)</f>
         <v/>
       </c>
+      <c r="G5" s="7">
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A5,Checklist!$H$2:$H$139,G$4)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -730,6 +752,10 @@
         <f>COUNTIFS(Checklist!$B$2:$B$139,$A6,Checklist!$H$2:$H$139,F$4)</f>
         <v/>
       </c>
+      <c r="G6" s="7">
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A6,Checklist!$H$2:$H$139,G$4)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -757,6 +783,10 @@
         <f>COUNTIFS(Checklist!$B$2:$B$139,$A7,Checklist!$H$2:$H$139,F$4)</f>
         <v/>
       </c>
+      <c r="G7" s="7">
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A7,Checklist!$H$2:$H$139,G$4)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -784,6 +814,10 @@
         <f>COUNTIFS(Checklist!$B$2:$B$139,$A8,Checklist!$H$2:$H$139,F$4)</f>
         <v/>
       </c>
+      <c r="G8" s="7">
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A8,Checklist!$H$2:$H$139,G$4)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -811,6 +845,10 @@
         <f>COUNTIFS(Checklist!$B$2:$B$139,$A9,Checklist!$H$2:$H$139,F$4)</f>
         <v/>
       </c>
+      <c r="G9" s="7">
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A9,Checklist!$H$2:$H$139,G$4)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -838,6 +876,10 @@
         <f>COUNTIFS(Checklist!$B$2:$B$139,$A10,Checklist!$H$2:$H$139,F$4)</f>
         <v/>
       </c>
+      <c r="G10" s="7">
+        <f>COUNTIFS(Checklist!$B$2:$B$139,$A10,Checklist!$H$2:$H$139,G$4)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -863,6 +905,10 @@
       </c>
       <c r="F11" s="8">
         <f>SUM(F5:F10)</f>
+        <v/>
+      </c>
+      <c r="G11" s="8">
+        <f>SUM(G5:G10)</f>
         <v/>
       </c>
     </row>
@@ -2486,7 +2532,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Testing team works through Medical_HRMS_Jameah_Test_Cases.xlsx and records results and bugs there.</t>
+          <t>Testing team works through Medical_HRMS_Jameah_Test_Cases.xlsx and records results and bugs there. Started 27 Oct with the test cases and both guides.</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -2501,12 +2547,12 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>HR-46</t>
+          <t>HR-46, HR-75</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr"/>
@@ -2517,7 +2563,7 @@
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr"/>
@@ -2972,7 +3018,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Give HR, managers and the testing team docs/guides/Medical_HRMS_Jameah_User_Guide.pdf, and the server admin docs/guides/Medical_HRMS_Jameah_Installation_Guide.pdf; collect their questions.</t>
+          <t>Give HR, managers and the testing team docs/guides/Medical_HRMS_Jameah_User_Guide.pdf, and the server admin docs/guides/Medical_HRMS_Jameah_Installation_Guide.pdf; collect their questions. 27 Oct: given to the testing team; still to give to HR, managers and the server admin.</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -2987,12 +3033,12 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>HR-74</t>
+          <t>HR-74, HR-75</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr"/>
@@ -3003,7 +3049,7 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr"/>
@@ -3015,18 +3061,21 @@
       <formula>$H2="Open"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
+      <formula>$H2="In progress"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
       <formula>$H2="Done"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="1">
       <formula>$H2="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="1">
+    <cfRule type="expression" priority="5" dxfId="4" stopIfTrue="1">
       <formula>$H2="Not needed"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="H2:H139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Open,Done,Blocked,Not needed"</formula1>
+      <formula1>"Open,In progress,Done,Blocked,Not needed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3039,7 +3088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3079,22 +3128,22 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>HR-37, HR-38, DEC-15, CL-38</t>
+          <t>HR-75, CL-23, CL-37</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
+          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
@@ -3116,12 +3165,12 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
+          <t>HR-37, HR-38, DEC-15, CL-38</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
+          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -3138,17 +3187,17 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Project tracking</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
+          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -3170,12 +3219,12 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -3192,17 +3241,17 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -3214,7 +3263,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -3224,12 +3273,12 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -3251,12 +3300,12 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -3273,17 +3322,17 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -3295,22 +3344,22 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -3327,17 +3376,17 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -3354,17 +3403,17 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -3376,7 +3425,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -3386,12 +3435,12 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -3403,7 +3452,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -3413,12 +3462,12 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -3430,25 +3479,52 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>Team</t>
         </is>

--- a/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Change Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Checklist'!$A$1:$L$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Checklist'!$A$1:$L$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -702,27 +702,27 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$139,$A5)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$142,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A5,Checklist!$H$2:$H$139,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A5,Checklist!$H$2:$H$142,C$4)</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A5,Checklist!$H$2:$H$139,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A5,Checklist!$H$2:$H$142,D$4)</f>
         <v/>
       </c>
       <c r="E5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A5,Checklist!$H$2:$H$139,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A5,Checklist!$H$2:$H$142,E$4)</f>
         <v/>
       </c>
       <c r="F5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A5,Checklist!$H$2:$H$139,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A5,Checklist!$H$2:$H$142,F$4)</f>
         <v/>
       </c>
       <c r="G5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A5,Checklist!$H$2:$H$139,G$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A5,Checklist!$H$2:$H$142,G$4)</f>
         <v/>
       </c>
     </row>
@@ -733,27 +733,27 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$139,$A6)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$142,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A6,Checklist!$H$2:$H$139,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A6,Checklist!$H$2:$H$142,C$4)</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A6,Checklist!$H$2:$H$139,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A6,Checklist!$H$2:$H$142,D$4)</f>
         <v/>
       </c>
       <c r="E6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A6,Checklist!$H$2:$H$139,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A6,Checklist!$H$2:$H$142,E$4)</f>
         <v/>
       </c>
       <c r="F6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A6,Checklist!$H$2:$H$139,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A6,Checklist!$H$2:$H$142,F$4)</f>
         <v/>
       </c>
       <c r="G6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A6,Checklist!$H$2:$H$139,G$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A6,Checklist!$H$2:$H$142,G$4)</f>
         <v/>
       </c>
     </row>
@@ -764,27 +764,27 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$139,$A7)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$142,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A7,Checklist!$H$2:$H$139,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A7,Checklist!$H$2:$H$142,C$4)</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A7,Checklist!$H$2:$H$139,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A7,Checklist!$H$2:$H$142,D$4)</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A7,Checklist!$H$2:$H$139,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A7,Checklist!$H$2:$H$142,E$4)</f>
         <v/>
       </c>
       <c r="F7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A7,Checklist!$H$2:$H$139,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A7,Checklist!$H$2:$H$142,F$4)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A7,Checklist!$H$2:$H$139,G$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A7,Checklist!$H$2:$H$142,G$4)</f>
         <v/>
       </c>
     </row>
@@ -795,27 +795,27 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$139,$A8)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$142,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A8,Checklist!$H$2:$H$139,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A8,Checklist!$H$2:$H$142,C$4)</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A8,Checklist!$H$2:$H$139,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A8,Checklist!$H$2:$H$142,D$4)</f>
         <v/>
       </c>
       <c r="E8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A8,Checklist!$H$2:$H$139,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A8,Checklist!$H$2:$H$142,E$4)</f>
         <v/>
       </c>
       <c r="F8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A8,Checklist!$H$2:$H$139,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A8,Checklist!$H$2:$H$142,F$4)</f>
         <v/>
       </c>
       <c r="G8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A8,Checklist!$H$2:$H$139,G$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A8,Checklist!$H$2:$H$142,G$4)</f>
         <v/>
       </c>
     </row>
@@ -826,27 +826,27 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$139,$A9)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$142,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A9,Checklist!$H$2:$H$139,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A9,Checklist!$H$2:$H$142,C$4)</f>
         <v/>
       </c>
       <c r="D9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A9,Checklist!$H$2:$H$139,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A9,Checklist!$H$2:$H$142,D$4)</f>
         <v/>
       </c>
       <c r="E9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A9,Checklist!$H$2:$H$139,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A9,Checklist!$H$2:$H$142,E$4)</f>
         <v/>
       </c>
       <c r="F9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A9,Checklist!$H$2:$H$139,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A9,Checklist!$H$2:$H$142,F$4)</f>
         <v/>
       </c>
       <c r="G9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A9,Checklist!$H$2:$H$139,G$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A9,Checklist!$H$2:$H$142,G$4)</f>
         <v/>
       </c>
     </row>
@@ -857,27 +857,27 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$139,$A10)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$142,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A10,Checklist!$H$2:$H$139,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A10,Checklist!$H$2:$H$142,C$4)</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A10,Checklist!$H$2:$H$139,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A10,Checklist!$H$2:$H$142,D$4)</f>
         <v/>
       </c>
       <c r="E10" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A10,Checklist!$H$2:$H$139,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A10,Checklist!$H$2:$H$142,E$4)</f>
         <v/>
       </c>
       <c r="F10" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A10,Checklist!$H$2:$H$139,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A10,Checklist!$H$2:$H$142,F$4)</f>
         <v/>
       </c>
       <c r="G10" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$139,$A10,Checklist!$H$2:$H$139,G$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$142,$A10,Checklist!$H$2:$H$142,G$4)</f>
         <v/>
       </c>
     </row>
@@ -923,7 +923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1599,37 +1599,37 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>CL-12</t>
+          <t>CL-41</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>3. Decisions</t>
+          <t>2. Check on the live server</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Ministry view and column names</t>
+          <t>Notification e-mails</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Ask which names the Jameah agent reads (HTML or schema V0.1), including the HTML spellings EnglishFourhtName and Summury.</t>
+          <t>After the e-mail account works (HR-47): an employee sends a request and HR rejects it with a reason; HR and the employee each get the e-mail and its link opens the request (TC-ESS-23).</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Ministry contact (Ms. Najah)</t>
+          <t>Testing team</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Before Jameah go-live</t>
+          <t>After HR-47</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>DEC-01</t>
+          <t>HR-25, HR-47</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -1640,12 +1640,12 @@
       <c r="I13" s="11" t="inlineStr"/>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr"/>
@@ -1653,7 +1653,7 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>CL-13</t>
+          <t>CL-12</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -1663,17 +1663,17 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Read-only database account for the Ministry</t>
+          <t>Ministry view and column names</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Create it with medical_hrms.jameah.views.grant_statements and give the Ministry the connection details.</t>
+          <t>Ask which names the Jameah agent reads (HTML or schema V0.1), including the HTML spellings EnglishFourhtName and Summury.</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Ministry contact (Ms. Najah)</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>JM-08</t>
+          <t>DEC-01</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>CL-14</t>
+          <t>CL-13</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -1717,17 +1717,17 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Jameah Settings and Student code decisions</t>
+          <t>Read-only database account for the Ministry</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Answers for DEC-02 - DEC-07, entered in Jameah Settings and the Code Map.</t>
+          <t>Create it with medical_hrms.jameah.views.grant_statements and give the Ministry the connection details.</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Academic Affairs</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>DEC-02 - DEC-07</t>
+          <t>JM-08</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>CL-15</t>
+          <t>CL-14</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Credit-hour definitions</t>
+          <t>Jameah Settings and Student code decisions</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Confirm Registered = this term's hours; Passed = earned + bridged plan hours.</t>
+          <t>Answers for DEC-02 - DEC-07, entered in Jameah Settings and the Code Map.</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>DEC-11</t>
+          <t>DEC-02 - DEC-07</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
@@ -1815,7 +1815,7 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>CL-16</t>
+          <t>CL-15</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Which faculty are sent</t>
+          <t>Credit-hour definitions</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Active Instructors only (as built), or also former (Left) ones.</t>
+          <t>Confirm Registered = this term's hours; Passed = earned + bridged plan hours.</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>DEC-12</t>
+          <t>DEC-11</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
@@ -1869,7 +1869,7 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>CL-17</t>
+          <t>CL-16</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Faculty status and contract codes</t>
+          <t>Which faculty are sent</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Pick the Ministry code for Faculty Status 'Active' and Contract Type 'Full Time' in Jameah Code Map.</t>
+          <t>Active Instructors only (as built), or also former (Left) ones.</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>DEC-13</t>
+          <t>DEC-12</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
@@ -1923,7 +1923,7 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>CL-18</t>
+          <t>CL-17</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -1933,27 +1933,27 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Demo employee EMP-00001</t>
+          <t>Faculty status and contract codes</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Complete it or delete it before go-live (it misses Ministry-mandatory fields).</t>
+          <t>Pick the Ministry code for Faculty Status 'Active' and Contract Type 'Full Time' in Jameah Code Map.</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Academic Affairs</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>Before go-live</t>
+          <t>Before Jameah go-live</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>HR-53</t>
+          <t>DEC-13</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
@@ -1977,22 +1977,22 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>CL-19</t>
+          <t>CL-18</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>4. HR data</t>
+          <t>3. Decisions</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Instructor data sheet</t>
+          <t>Demo employee EMP-00001</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Fill the Instructor sheet so the existing Instructors are linked to Employees; the Faculty views fill in as they are.</t>
+          <t>Complete it or delete it before go-live (it misses Ministry-mandatory fields).</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Before Jameah go-live</t>
+          <t>Before go-live</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>HR-55</t>
+          <t>HR-53</t>
         </is>
       </c>
       <c r="H20" s="11" t="inlineStr">
@@ -2031,7 +2031,7 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>CL-20</t>
+          <t>CL-19</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -2041,12 +2041,12 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Non-academic staff data sheet</t>
+          <t>Instructor data sheet</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Employees Missing Ministry Data report -&gt; Download Data Sheet -&gt; fill the red cells -&gt; Check -&gt; Import.</t>
+          <t>Fill the Instructor sheet so the existing Instructors are linked to Employees; the Faculty views fill in as they are.</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>HR-50</t>
+          <t>HR-55</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
@@ -2085,7 +2085,7 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>CL-21</t>
+          <t>CL-20</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -2095,12 +2095,12 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Academic Holiday List</t>
+          <t>Non-academic staff data sheet</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Set it in HR Settings &gt; Academic Schedules &amp; Presence.</t>
+          <t>Employees Missing Ministry Data report -&gt; Download Data Sheet -&gt; fill the red cells -&gt; Check -&gt; Import.</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Before UAT</t>
+          <t>Before Jameah go-live</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>HR-57</t>
+          <t>HR-50</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>CL-38</t>
+          <t>CL-21</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -2149,27 +2149,27 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Exam committees with proctors</t>
+          <t>Academic Holiday List</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Enter the exam committees (date, time, room) with their proctors; until then Proctor Schedules is empty. Needed to review HR requirement 2.</t>
+          <t>Set it in HR Settings &gt; Academic Schedules &amp; Presence.</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Academic Affairs</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Before the HR review meeting</t>
+          <t>Before UAT</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>HR-37</t>
+          <t>HR-57</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
@@ -2180,12 +2180,12 @@
       <c r="I23" s="11" t="inlineStr"/>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>CL-28</t>
+          <t>CL-38</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -2203,27 +2203,27 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Leave period for Al Riyada College</t>
+          <t>Exam committees with proctors</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>HR Portal &gt; Leave &gt; Yearly setup 1: Leave Period for this year, company Al Riyada College, tick Is Active.</t>
+          <t>Enter the exam committees (date, time, room) with their proctors; until then Proctor Schedules is empty. Needed to review HR requirement 2.</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Academic Affairs</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Before UAT</t>
+          <t>Before the HR review meeting</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>HR-69</t>
+          <t>HR-37</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
@@ -2234,12 +2234,12 @@
       <c r="I24" s="11" t="inlineStr"/>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="L24" s="12" t="inlineStr"/>
@@ -2247,7 +2247,7 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>CL-29</t>
+          <t>CL-40</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Holiday list for Al Riyada College</t>
+          <t>Leave e-mail templates</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Step 2: Holiday List with the official holidays and weekends; set it as the default holiday list on the Company.</t>
+          <t>HR Settings -&gt; Leave Approval Notification Template = Leave Approval Notification, Leave Status Notification Template = Leave Status Notification (both come with HRMS). Without them leave approvers and employees get no leave e-mails.</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>HR-69, DEC-10</t>
+          <t>HR-25</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
@@ -2288,12 +2288,12 @@
       <c r="I25" s="11" t="inlineStr"/>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr"/>
@@ -2301,7 +2301,7 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>CL-30</t>
+          <t>CL-28</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Leave approvers</t>
+          <t>Leave period for Al Riyada College</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Step 5: set the leave approver on each Department (Leave Approvers table) or on each Employee. Check the Leave setup check on the live server for how many have none.</t>
+          <t>HR Portal &gt; Leave &gt; Yearly setup 1: Leave Period for this year, company Al Riyada College, tick Is Active.</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="L26" s="12" t="inlineStr"/>
@@ -2355,7 +2355,7 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>CL-31</t>
+          <t>CL-29</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -2365,12 +2365,12 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Annual leave balances</t>
+          <t>Holiday list for Al Riyada College</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Steps 3-4: submit the annual leave policy (21 or 30 days) and assign it with Leave Control Panel; the Leave setup check turns green.</t>
+          <t>Step 2: Holiday List with the official holidays and weekends; set it as the default holiday list on the Company.</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>HR-69</t>
+          <t>HR-69, DEC-10</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>CL-32</t>
+          <t>CL-30</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -2419,17 +2419,17 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Sick Leave policy</t>
+          <t>Leave approvers</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Review and submit 'Medical HRMS - Sick Leave (3 Pay Stages, Separate Sick Year)'; Finance checks the 75% pay on a salary slip.</t>
+          <t>Step 5: set the leave approver on each Department (Leave Approvers table) or on each Employee. Check the Leave setup check on the live server for how many have none.</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>HR + Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>HR-20, DEC-14</t>
+          <t>HR-69</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr"/>
@@ -2463,7 +2463,7 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>CL-22</t>
+          <t>CL-31</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Attendance devices</t>
+          <t>Annual leave balances</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Connect the devices so Faculty After 4 PM uses real check-out times.</t>
+          <t>Steps 3-4: submit the annual leave policy (21 or 30 days) and assign it with Leave Control Panel; the Leave setup check turns green.</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>HR + IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>Later</t>
+          <t>Before UAT</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>HR-56</t>
+          <t>HR-69</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
@@ -2504,12 +2504,12 @@
       <c r="I29" s="11" t="inlineStr"/>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr"/>
@@ -2517,53 +2517,53 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>CL-23</t>
+          <t>CL-32</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>5. Reviews and testing</t>
+          <t>4. HR data</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Run the test cases</t>
+          <t>Sick Leave policy</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Testing team works through Medical_HRMS_Jameah_Test_Cases.xlsx and records results and bugs there. Started 27 Oct with the test cases and both guides.</t>
+          <t>Review and submit 'Medical HRMS - Sick Leave (3 Pay Stages, Separate Sick Year)'; Finance checks the 75% pay on a salary slip.</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Testing team</t>
+          <t>HR + Finance</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>UAT</t>
+          <t>Before UAT</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>HR-46, HR-75</t>
+          <t>HR-20, DEC-14</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr"/>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>27 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr"/>
@@ -2571,37 +2571,37 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>CL-24</t>
+          <t>CL-22</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>5. Reviews and testing</t>
+          <t>4. HR data</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Arabic labels</t>
+          <t>Attendance devices</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>An Arabic speaker reads the HR / Employee Portal pages in Arabic and lists wording to change, including the 114 new leave texts (22 Oct).</t>
+          <t>Connect the devices so Faculty After 4 PM uses real check-out times.</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Project owner</t>
+          <t>HR + IT</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>UAT</t>
+          <t>Later</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>HR-66, HR-68</t>
+          <t>HR-56</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr"/>
@@ -2625,7 +2625,7 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>CL-25</t>
+          <t>CL-23</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -2635,17 +2635,17 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Portal design approval</t>
+          <t>Run the test cases</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>Client confirms the new HR Portal / Employee Portal look.</t>
+          <t>Testing team works through Medical_HRMS_Jameah_Test_Cases.xlsx and records results and bugs there. Started 27 Oct with the test cases and both guides.</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Project owner</t>
+          <t>Testing team</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -2655,12 +2655,12 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-46, HR-75</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr"/>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr"/>
@@ -2679,7 +2679,7 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>CL-33</t>
+          <t>CL-24</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Leave flow UAT</t>
+          <t>Arabic labels</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>An employee and their manager go through TC-LV-09 - TC-LV-17: plan, apply now, approve, return (also after sick leave).</t>
+          <t>An Arabic speaker reads the HR / Employee Portal pages in Arabic and lists wording to change, including the 114 new leave texts (22 Oct).</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Testing team</t>
+          <t>Project owner</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>HR-68</t>
+          <t>HR-66, HR-68</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
@@ -2720,7 +2720,7 @@
       <c r="I33" s="11" t="inlineStr"/>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
@@ -2733,7 +2733,7 @@
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>CL-26</t>
+          <t>CL-25</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -2743,17 +2743,17 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Arabic interface</t>
+          <t>Portal design approval</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>Switch to AR and repeat a few test cases (HR Portal, Employee Portal, application form).</t>
+          <t>Client confirms the new HR Portal / Employee Portal look.</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>Testing team</t>
+          <t>Project owner</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
@@ -2787,7 +2787,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>CL-27</t>
+          <t>CL-33</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -2797,27 +2797,27 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Developer copy of the education app up to date</t>
+          <t>Leave flow UAT</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>On the development machine the education app checkout is behind its master branch; update it before testing there (git pull --ff-only).</t>
+          <t>An employee and their manager go through TC-LV-09 - TC-LV-17: plan, apply now, approve, return (also after sick leave).</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Project owner</t>
+          <t>Testing team</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>Now</t>
+          <t>UAT</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HR-68</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
@@ -2828,12 +2828,12 @@
       <c r="I35" s="11" t="inlineStr"/>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr"/>
@@ -2841,37 +2841,37 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>CL-34</t>
+          <t>CL-26</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>6. Team and repository</t>
+          <t>5. Reviews and testing</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Delete the merged branches on GitHub</t>
+          <t>Arabic interface</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>After UAT: feature/uat-2026-10-22, feature/hr-portal-design, feature/jameah-ministry-views, fix/hrm-e2e-approval-permission-bugs, ministry-lookup, employee-applicant (all merged into develop; their history stays in develop).</t>
+          <t>Switch to AR and repeat a few test cases (HR Portal, Employee Portal, application form).</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Project owner</t>
+          <t>Testing team</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>After UAT</t>
+          <t>UAT</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>HR-71</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
@@ -2882,12 +2882,12 @@
       <c r="I36" s="11" t="inlineStr"/>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="L36" s="12" t="inlineStr"/>
@@ -2895,22 +2895,22 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>CL-35</t>
+          <t>CL-27</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>6. Team and repository</t>
+          <t>5. Reviews and testing</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Assign the open tasks</t>
+          <t>Developer copy of the education app up to date</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Task Tracker, Tasks sheet: pick who each open task is given to in the Assigned to column (dropdown; e.g. HR-73, HR-16, HR-17, HR-25, JM-15, JM-19).</t>
+          <t>On the development machine the education app checkout is behind its master branch; update it before testing there (git pull --ff-only).</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>HR-73</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
@@ -2936,7 +2936,7 @@
       <c r="I37" s="11" t="inlineStr"/>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>CL-36</t>
+          <t>CL-34</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -2959,27 +2959,27 @@
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Checks before every release</t>
+          <t>Delete the merged branches on GitHub</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>python3 tests/checks/files.py; fx.py tests/checks/site.py; python3 tests/checks/api_methods.py; then the browser suite (tests/e2e/README.md). All must pass.</t>
+          <t>After UAT: feature/uat-2026-10-22, feature/hr-portal-design, feature/jameah-ministry-views, fix/hrm-e2e-approval-permission-bugs, ministry-lookup, employee-applicant (all merged into develop; their history stays in develop).</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Developer (Abdul Hakeem)</t>
+          <t>Project owner</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>Every release</t>
+          <t>After UAT</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>HR-72</t>
+          <t>HR-71</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
@@ -3003,22 +3003,22 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>CL-37</t>
+          <t>CL-35</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>5. Reviews and testing</t>
+          <t>6. Team and repository</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Share the guides</t>
+          <t>Assign the open tasks</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Give HR, managers and the testing team docs/guides/Medical_HRMS_Jameah_User_Guide.pdf, and the server admin docs/guides/Medical_HRMS_Jameah_Installation_Guide.pdf; collect their questions. 27 Oct: given to the testing team; still to give to HR, managers and the server admin.</t>
+          <t>Task Tracker, Tasks sheet: pick who each open task is given to in the Assigned to column (dropdown; e.g. HR-73, HR-16, HR-17, HR-25, JM-15, JM-19).</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>UAT</t>
+          <t>Now</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>HR-74, HR-75</t>
+          <t>HR-73</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr"/>
@@ -3049,14 +3049,176 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="L39" s="12" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>CL-36</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>6. Team and repository</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Checks before every release</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>python3 tests/checks/files.py; fx.py tests/checks/site.py; python3 tests/checks/api_methods.py; then the browser suite (tests/e2e/README.md). All must pass.</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Developer (Abdul Hakeem)</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>Every release</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>HR-72</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr"/>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="L40" s="12" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>CL-37</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>5. Reviews and testing</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Share the guides</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Give HR, managers and the testing team docs/guides/Medical_HRMS_Jameah_User_Guide.pdf, and the server admin docs/guides/Medical_HRMS_Jameah_Installation_Guide.pdf; collect their questions. 27 Oct: given to the testing team; still to give to HR, managers and the server admin.</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>UAT</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>HR-74, HR-75</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr"/>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
           <t>27 Oct 2026</t>
         </is>
       </c>
-      <c r="L39" s="12" t="inlineStr"/>
+      <c r="L41" s="12" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>CL-39</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>5. Reviews and testing</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Round 2 document to the testing team</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Put Round 2 on their test server first (CL-01, migrate), then give them docs/guides/Medical_HRMS_Round_2_Whats_New.pdf and the Test Cases workbook (filter Round = Round 2).</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>HR-76</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr"/>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>27 Oct 2026</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>27 Oct 2026</t>
+        </is>
+      </c>
+      <c r="L42" s="12" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L39"/>
-  <conditionalFormatting sqref="H2:H139">
+  <autoFilter ref="A1:L42"/>
+  <conditionalFormatting sqref="H2:H142">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>$H2="Open"</formula>
     </cfRule>
@@ -3074,7 +3236,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H2:H142" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Open,In progress,Done,Blocked,Not needed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3088,7 +3250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3133,17 +3295,17 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Round 2</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>HR-75, CL-23, CL-37</t>
+          <t>HR-16, HR-24, HR-25, HR-48, HR-76, HR-77, B-26, B-56, B-57, DEC-16, CL-39 - CL-41, TC-APR-02, TC-APR-09 - TC-APR-13, TC-ESS-17 - TC-ESS-23, TC-EMP-13, TC-EMP-14, TC-LV-18</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
+          <t>Round 2: employees change, send or delete their drafts and send a rejected request again; rejecting needs a reason, which the employee reads with the request's history; notifications in the bell (and e-mail where the mail account works) for HR on new requests and for the employee at every later step; the Instructor and Academic Advisor forms save after an Employee is picked (B-26, B-56); amounts say SAR; the bell shows the time as text (B-57). New: Round column in the Test Cases workbook, the Round 2 document for the testers, User Guide and Installation Guide updated. Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
@@ -3155,22 +3317,22 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>HR-37, HR-38, DEC-15, CL-38</t>
+          <t>HR-75, CL-23, CL-37</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
+          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -3192,12 +3354,12 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
+          <t>HR-37, HR-38, DEC-15, CL-38</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
+          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -3214,17 +3376,17 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Project tracking</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
+          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -3246,12 +3408,12 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -3268,17 +3430,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -3290,7 +3452,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -3300,12 +3462,12 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -3327,12 +3489,12 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -3349,17 +3511,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -3371,22 +3533,22 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -3403,17 +3565,17 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -3430,17 +3592,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -3452,7 +3614,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -3462,12 +3624,12 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -3479,7 +3641,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -3489,12 +3651,12 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -3506,25 +3668,52 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>Team</t>
         </is>

--- a/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
@@ -3250,7 +3250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3295,17 +3295,17 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Round 2</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>HR-16, HR-24, HR-25, HR-48, HR-76, HR-77, B-26, B-56, B-57, DEC-16, CL-39 - CL-41, TC-APR-02, TC-APR-09 - TC-APR-13, TC-ESS-17 - TC-ESS-23, TC-EMP-13, TC-EMP-14, TC-LV-18</t>
+          <t>HR-76</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>Round 2: employees change, send or delete their drafts and send a rejected request again; rejecting needs a reason, which the employee reads with the request's history; notifications in the bell (and e-mail where the mail account works) for HR on new requests and for the employee at every later step; the Instructor and Academic Advisor forms save after an Employee is picked (B-26, B-56); amounts say SAR; the bell shows the time as text (B-57). New: Round column in the Test Cases workbook, the Round 2 document for the testers, User Guide and Installation Guide updated. Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
+          <t>QA cleanup stops the unsent e-mails of removed QA records (status Error) instead of deleting them: the e-mail job could be sending them at that moment and logged 'Email Queue ... not found'.</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
@@ -3322,17 +3322,17 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Round 2</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>HR-75, CL-23, CL-37</t>
+          <t>HR-16, HR-24, HR-25, HR-48, HR-76, HR-77, B-26, B-56, B-57, DEC-16, CL-39 - CL-41, TC-APR-02, TC-APR-09 - TC-APR-13, TC-ESS-17 - TC-ESS-23, TC-EMP-13, TC-EMP-14, TC-LV-18</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
+          <t>Round 2: employees change, send or delete their drafts and send a rejected request again; rejecting needs a reason, which the employee reads with the request's history; notifications in the bell (and e-mail where the mail account works) for HR on new requests and for the employee at every later step; the Instructor and Academic Advisor forms save after an Employee is picked (B-26, B-56); amounts say SAR; the bell shows the time as text (B-57). New: Round column in the Test Cases workbook, the Round 2 document for the testers, User Guide and Installation Guide updated. Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -3344,22 +3344,22 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>HR-37, HR-38, DEC-15, CL-38</t>
+          <t>HR-75, CL-23, CL-37</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
+          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
+          <t>HR-37, HR-38, DEC-15, CL-38</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
+          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -3403,17 +3403,17 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Project tracking</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
+          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -3457,17 +3457,17 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -3479,7 +3479,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -3538,17 +3538,17 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -3560,22 +3560,22 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -3592,17 +3592,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -3619,17 +3619,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -3641,7 +3641,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -3668,7 +3668,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -3678,12 +3678,12 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -3695,25 +3695,52 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>Team</t>
         </is>

--- a/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
@@ -1614,7 +1614,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>After the e-mail account works (HR-47): an employee sends a request and HR rejects it with a reason; HR and the employee each get the e-mail and its link opens the request (TC-ESS-23).</t>
+          <t>After the e-mail account works (HR-47): an employee sends a request and HR rejects it with a reason; HR and the employee each get the e-mail and its link opens the request (TC-ESS-23); the same for a leave application (TC-LV-19). The text and links were already checked on the test copy with a local mail catcher (27 Oct), so this is about delivery from the college account. Leave e-mails are sent in the name of the person who acted.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>HR Settings -&gt; Leave Approval Notification Template = Leave Approval Notification, Leave Status Notification Template = Leave Status Notification (both come with HRMS). Without them leave approvers and employees get no leave e-mails.</t>
+          <t>Set by the migrate (CL-02): HR Settings -&gt; Leave Approval / Leave Status Notification Template = the two '(Medical HRMS)' templates, only where empty (a template HR chose is kept). The employee's e-mail has the rejection reason and opens the application on the Employee Portal. HR can change the wording in Email Template.</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Developer (Abdul Hakeem)</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -2282,10 +2282,14 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I25" s="11" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>27 Oct 2026</t>
+        </is>
+      </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
           <t>27 Oct 2026</t>
@@ -3250,7 +3254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3295,17 +3299,17 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Leave e-mails</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>HR-76</t>
+          <t>HR-25, HR-76, DEC-16, CL-40, CL-41, TC-LV-19</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>QA cleanup stops the unsent e-mails of removed QA records (status Error) instead of deleting them: the e-mail job could be sending them at that moment and logged 'Email Queue ... not found'.</t>
+          <t>DEC-16 answered: every HR User and HR Manager login is told about new requests (as built). Leave e-mails: two Medical HRMS templates (the employee's has the rejection reason and opens the application on the Employee Portal), chosen in HR Settings by the migrate where empty - CL-40 done, no HR step left. Checked on this copy with a local mail catcher (nothing left the machine): 7 e-mails with the right text and links; unit test added (11 in test_request_flow). Round 2 document, User Guide and Installation Guide updated; new case TC-LV-19.</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
@@ -3322,17 +3326,17 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Round 2</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>HR-16, HR-24, HR-25, HR-48, HR-76, HR-77, B-26, B-56, B-57, DEC-16, CL-39 - CL-41, TC-APR-02, TC-APR-09 - TC-APR-13, TC-ESS-17 - TC-ESS-23, TC-EMP-13, TC-EMP-14, TC-LV-18</t>
+          <t>HR-76</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Round 2: employees change, send or delete their drafts and send a rejected request again; rejecting needs a reason, which the employee reads with the request's history; notifications in the bell (and e-mail where the mail account works) for HR on new requests and for the employee at every later step; the Instructor and Academic Advisor forms save after an Employee is picked (B-26, B-56); amounts say SAR; the bell shows the time as text (B-57). New: Round column in the Test Cases workbook, the Round 2 document for the testers, User Guide and Installation Guide updated. Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
+          <t>QA cleanup stops the unsent e-mails of removed QA records (status Error) instead of deleting them: the e-mail job could be sending them at that moment and logged 'Email Queue ... not found'.</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -3349,17 +3353,17 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Round 2</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>HR-75, CL-23, CL-37</t>
+          <t>HR-16, HR-24, HR-25, HR-48, HR-76, HR-77, B-26, B-56, B-57, DEC-16, CL-39 - CL-41, TC-APR-02, TC-APR-09 - TC-APR-13, TC-ESS-17 - TC-ESS-23, TC-EMP-13, TC-EMP-14, TC-LV-18</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
+          <t>Round 2: employees change, send or delete their drafts and send a rejected request again; rejecting needs a reason, which the employee reads with the request's history; notifications in the bell (and e-mail where the mail account works) for HR on new requests and for the employee at every later step; the Instructor and Academic Advisor forms save after an Employee is picked (B-26, B-56); amounts say SAR; the bell shows the time as text (B-57). New: Round column in the Test Cases workbook, the Round 2 document for the testers, User Guide and Installation Guide updated. Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -3371,22 +3375,22 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>HR-37, HR-38, DEC-15, CL-38</t>
+          <t>HR-75, CL-23, CL-37</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
+          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -3408,12 +3412,12 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
+          <t>HR-37, HR-38, DEC-15, CL-38</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
+          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -3430,17 +3434,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Project tracking</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
+          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -3462,12 +3466,12 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -3484,17 +3488,17 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -3506,7 +3510,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -3516,12 +3520,12 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -3543,12 +3547,12 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -3565,17 +3569,17 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -3587,22 +3591,22 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -3619,17 +3623,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -3646,17 +3650,17 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -3668,7 +3672,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -3678,12 +3682,12 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -3695,7 +3699,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -3705,12 +3709,12 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -3722,25 +3726,52 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>Team</t>
         </is>

--- a/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Checklist.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Change Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Checklist'!$A$1:$L$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Checklist'!$A$1:$L$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -702,27 +702,27 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$142,$A5)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$143,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A5,Checklist!$H$2:$H$142,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A5,Checklist!$H$2:$H$143,C$4)</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A5,Checklist!$H$2:$H$142,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A5,Checklist!$H$2:$H$143,D$4)</f>
         <v/>
       </c>
       <c r="E5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A5,Checklist!$H$2:$H$142,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A5,Checklist!$H$2:$H$143,E$4)</f>
         <v/>
       </c>
       <c r="F5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A5,Checklist!$H$2:$H$142,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A5,Checklist!$H$2:$H$143,F$4)</f>
         <v/>
       </c>
       <c r="G5" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A5,Checklist!$H$2:$H$142,G$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A5,Checklist!$H$2:$H$143,G$4)</f>
         <v/>
       </c>
     </row>
@@ -733,27 +733,27 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$142,$A6)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$143,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A6,Checklist!$H$2:$H$142,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A6,Checklist!$H$2:$H$143,C$4)</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A6,Checklist!$H$2:$H$142,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A6,Checklist!$H$2:$H$143,D$4)</f>
         <v/>
       </c>
       <c r="E6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A6,Checklist!$H$2:$H$142,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A6,Checklist!$H$2:$H$143,E$4)</f>
         <v/>
       </c>
       <c r="F6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A6,Checklist!$H$2:$H$142,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A6,Checklist!$H$2:$H$143,F$4)</f>
         <v/>
       </c>
       <c r="G6" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A6,Checklist!$H$2:$H$142,G$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A6,Checklist!$H$2:$H$143,G$4)</f>
         <v/>
       </c>
     </row>
@@ -764,27 +764,27 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$142,$A7)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$143,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A7,Checklist!$H$2:$H$142,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A7,Checklist!$H$2:$H$143,C$4)</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A7,Checklist!$H$2:$H$142,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A7,Checklist!$H$2:$H$143,D$4)</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A7,Checklist!$H$2:$H$142,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A7,Checklist!$H$2:$H$143,E$4)</f>
         <v/>
       </c>
       <c r="F7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A7,Checklist!$H$2:$H$142,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A7,Checklist!$H$2:$H$143,F$4)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A7,Checklist!$H$2:$H$142,G$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A7,Checklist!$H$2:$H$143,G$4)</f>
         <v/>
       </c>
     </row>
@@ -795,27 +795,27 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$142,$A8)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$143,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A8,Checklist!$H$2:$H$142,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A8,Checklist!$H$2:$H$143,C$4)</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A8,Checklist!$H$2:$H$142,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A8,Checklist!$H$2:$H$143,D$4)</f>
         <v/>
       </c>
       <c r="E8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A8,Checklist!$H$2:$H$142,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A8,Checklist!$H$2:$H$143,E$4)</f>
         <v/>
       </c>
       <c r="F8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A8,Checklist!$H$2:$H$142,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A8,Checklist!$H$2:$H$143,F$4)</f>
         <v/>
       </c>
       <c r="G8" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A8,Checklist!$H$2:$H$142,G$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A8,Checklist!$H$2:$H$143,G$4)</f>
         <v/>
       </c>
     </row>
@@ -826,27 +826,27 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$142,$A9)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$143,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A9,Checklist!$H$2:$H$142,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A9,Checklist!$H$2:$H$143,C$4)</f>
         <v/>
       </c>
       <c r="D9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A9,Checklist!$H$2:$H$142,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A9,Checklist!$H$2:$H$143,D$4)</f>
         <v/>
       </c>
       <c r="E9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A9,Checklist!$H$2:$H$142,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A9,Checklist!$H$2:$H$143,E$4)</f>
         <v/>
       </c>
       <c r="F9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A9,Checklist!$H$2:$H$142,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A9,Checklist!$H$2:$H$143,F$4)</f>
         <v/>
       </c>
       <c r="G9" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A9,Checklist!$H$2:$H$142,G$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A9,Checklist!$H$2:$H$143,G$4)</f>
         <v/>
       </c>
     </row>
@@ -857,27 +857,27 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Checklist!$B$2:$B$142,$A10)</f>
+        <f>COUNTIF(Checklist!$B$2:$B$143,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A10,Checklist!$H$2:$H$142,C$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A10,Checklist!$H$2:$H$143,C$4)</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A10,Checklist!$H$2:$H$142,D$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A10,Checklist!$H$2:$H$143,D$4)</f>
         <v/>
       </c>
       <c r="E10" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A10,Checklist!$H$2:$H$142,E$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A10,Checklist!$H$2:$H$143,E$4)</f>
         <v/>
       </c>
       <c r="F10" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A10,Checklist!$H$2:$H$142,F$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A10,Checklist!$H$2:$H$143,F$4)</f>
         <v/>
       </c>
       <c r="G10" s="7">
-        <f>COUNTIFS(Checklist!$B$2:$B$142,$A10,Checklist!$H$2:$H$142,G$4)</f>
+        <f>COUNTIFS(Checklist!$B$2:$B$143,$A10,Checklist!$H$2:$H$143,G$4)</f>
         <v/>
       </c>
     </row>
@@ -923,7 +923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3220,9 +3220,63 @@
       </c>
       <c r="L42" s="12" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>CL-42</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>5. Reviews and testing</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Round 3 document to the testing team</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>With Round 2 (same deploy: CL-01 - CL-03, build and clear-cache): give them docs/guides/Medical_HRMS_Round_3_Whats_New.pdf (filter Round = Round 3), and link their instructor / head-of-department test logins to Employee records first, or they see no card.</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>HR-11, HR-78</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr"/>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>27 Oct 2026</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>27 Oct 2026</t>
+        </is>
+      </c>
+      <c r="L43" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L42"/>
-  <conditionalFormatting sqref="H2:H142">
+  <autoFilter ref="A1:L43"/>
+  <conditionalFormatting sqref="H2:H143">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>$H2="Open"</formula>
     </cfRule>
@@ -3240,7 +3294,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H142" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H2:H143" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Open,In progress,Done,Blocked,Not needed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3254,7 +3308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3299,17 +3353,17 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Leave e-mails</t>
+          <t>Round 3</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>HR-25, HR-76, DEC-16, CL-40, CL-41, TC-LV-19</t>
+          <t>HR-11, HR-78, B-58, B-59, CL-42, TC-STF-01 - TC-STF-10</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>DEC-16 answered: every HR User and HR Manager login is told about new requests (as built). Leave e-mails: two Medical HRMS templates (the employee's has the rejection reason and opens the application on the Employee Portal), chosen in HR Settings by the migrate where empty - CL-40 done, no HR step left. Checked on this copy with a local mail catcher (nothing left the machine): 7 e-mails with the right text and links; unit test added (11 in test_request_flow). Round 2 document, User Guide and Installation Guide updated; new case TC-LV-19.</t>
+          <t>Round 3: a My HR card on the education staff dashboards (Instructor, Department Head, Dean, Vice Deans, IT, Academic Operations, Student Affairs, Admission, Finance, Clinical, Advisor) for logins linked to an Employee record: leave balances and what's next, the latest requests, Apply for Leave, New Request and View, with the Employee Portal's own windows (now shared: public/js/self_service.js). Nothing in the education app changed. New: the Round 3 document for the testers, 10 test cases (Round 3), User Guide section 2.11, Installation Guide troubleshooting, QA logins qa.hod, qa.dean, qa.staff.nolink. Tested: 111/111 browser checks (10 new: SHR-01 - SHR-10), 53 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; card placement checked on 11 staff dashboards (8 with figures, Advisor under its heading, Dean and Department Head in the browser tests); Error Log: only test-caused entries, removed. The full run caught a script error of the card on every other page (B-59), fixed before release.</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
@@ -3326,17 +3380,17 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Leave e-mails</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>HR-76</t>
+          <t>HR-25, HR-76, DEC-16, CL-40, CL-41, TC-LV-19</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>QA cleanup stops the unsent e-mails of removed QA records (status Error) instead of deleting them: the e-mail job could be sending them at that moment and logged 'Email Queue ... not found'.</t>
+          <t>DEC-16 answered: every HR User and HR Manager login is told about new requests (as built). Leave e-mails: two Medical HRMS templates (the employee's has the rejection reason and opens the application on the Employee Portal), chosen in HR Settings by the migrate where empty - CL-40 done, no HR step left. Checked on this copy with a local mail catcher (nothing left the machine): 7 e-mails with the right text and links; unit test added (11 in test_request_flow). Round 2 document, User Guide and Installation Guide updated; new case TC-LV-19.</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -3353,17 +3407,17 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Round 2</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>HR-16, HR-24, HR-25, HR-48, HR-76, HR-77, B-26, B-56, B-57, DEC-16, CL-39 - CL-41, TC-APR-02, TC-APR-09 - TC-APR-13, TC-ESS-17 - TC-ESS-23, TC-EMP-13, TC-EMP-14, TC-LV-18</t>
+          <t>HR-76</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Round 2: employees change, send or delete their drafts and send a rejected request again; rejecting needs a reason, which the employee reads with the request's history; notifications in the bell (and e-mail where the mail account works) for HR on new requests and for the employee at every later step; the Instructor and Academic Advisor forms save after an Employee is picked (B-26, B-56); amounts say SAR; the bell shows the time as text (B-57). New: Round column in the Test Cases workbook, the Round 2 document for the testers, User Guide and Installation Guide updated. Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
+          <t>QA cleanup stops the unsent e-mails of removed QA records (status Error) instead of deleting them: the e-mail job could be sending them at that moment and logged 'Email Queue ... not found'.</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -3380,17 +3434,17 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Round 2</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>HR-75, CL-23, CL-37</t>
+          <t>HR-16, HR-24, HR-25, HR-48, HR-76, HR-77, B-26, B-56, B-57, DEC-16, CL-39 - CL-41, TC-APR-02, TC-APR-09 - TC-APR-13, TC-ESS-17 - TC-ESS-23, TC-EMP-13, TC-EMP-14, TC-LV-18</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
+          <t>Round 2: employees change, send or delete their drafts and send a rejected request again; rejecting needs a reason, which the employee reads with the request's history; notifications in the bell (and e-mail where the mail account works) for HR on new requests and for the employee at every later step; the Instructor and Academic Advisor forms save after an Employee is picked (B-26, B-56); amounts say SAR; the bell shows the time as text (B-57). New: Round column in the Test Cases workbook, the Round 2 document for the testers, User Guide and Installation Guide updated. Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -3402,22 +3456,22 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>HR-37, HR-38, DEC-15, CL-38</t>
+          <t>HR-75, CL-23, CL-37</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
+          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -3439,12 +3493,12 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
+          <t>HR-37, HR-38, DEC-15, CL-38</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
+          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -3461,17 +3515,17 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Project tracking</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
+          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -3493,12 +3547,12 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -3515,17 +3569,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -3537,7 +3591,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -3547,12 +3601,12 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -3574,12 +3628,12 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -3596,17 +3650,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -3618,22 +3672,22 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -3650,17 +3704,17 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -3677,17 +3731,17 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -3699,7 +3753,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -3709,12 +3763,12 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -3726,7 +3780,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -3736,12 +3790,12 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -3753,25 +3807,52 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
